--- a/data/trans_dic/P19D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,24</t>
+          <t>4,67; 9,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,34; 18,43</t>
+          <t>12,31; 18,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 13,62</t>
+          <t>8,14; 13,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,53</t>
+          <t>7,3; 12,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,33</t>
+          <t>3,48; 7,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,19</t>
+          <t>9,32; 15,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,4</t>
+          <t>6,53; 11,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,66</t>
+          <t>4,2; 6,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,79</t>
+          <t>4,64; 7,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,78</t>
+          <t>11,78; 15,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,72</t>
+          <t>7,94; 11,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 9,05</t>
+          <t>6,1; 8,9</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,92</t>
+          <t>5,04; 8,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,46; 17,42</t>
+          <t>12,16; 17,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,34</t>
+          <t>6,28; 10,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 60,3</t>
+          <t>6,68; 10,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,46</t>
+          <t>4,99; 8,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 14,24</t>
+          <t>9,93; 14,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,52</t>
+          <t>6,83; 10,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,18</t>
+          <t>4,79; 7,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,93</t>
+          <t>5,38; 8,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 15,05</t>
+          <t>11,7; 14,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,91</t>
+          <t>7,06; 9,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 43,19</t>
+          <t>6,13; 8,3</t>
         </is>
       </c>
     </row>
@@ -944,34 +944,34 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>7,63%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>12,15%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,09</t>
+          <t>6,56; 11,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 17,58</t>
+          <t>11,95; 17,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,49</t>
+          <t>6,4; 11,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,74</t>
+          <t>5,86; 10,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,6</t>
+          <t>4,58; 8,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,98; 12,91</t>
+          <t>7,77; 12,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,83</t>
+          <t>5,27; 9,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,54</t>
+          <t>3,64; 6,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,35</t>
+          <t>6,29; 9,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 14,27</t>
+          <t>10,14; 14,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,77</t>
+          <t>6,6; 9,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,15</t>
+          <t>5,14; 8,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,68</t>
+          <t>5,22; 8,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,01</t>
+          <t>8,23; 12,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,13</t>
+          <t>7,8; 11,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,87</t>
+          <t>6,69; 10,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,18</t>
+          <t>6,32; 10,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,89</t>
+          <t>7,99; 12,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 12,39</t>
+          <t>8,36; 12,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,54</t>
+          <t>5,46; 7,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,99</t>
+          <t>6,18; 8,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,74</t>
+          <t>8,63; 11,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 11,69</t>
+          <t>8,63; 11,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 8,87</t>
+          <t>6,48; 8,77</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,27</t>
+          <t>6,27; 8,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,23; 14,88</t>
+          <t>12,34; 15,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,49</t>
+          <t>8,12; 10,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,87; 36,7</t>
+          <t>7,56; 9,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,72</t>
+          <t>5,82; 7,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,12</t>
+          <t>9,93; 12,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 9,94</t>
+          <t>7,83; 9,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,22</t>
+          <t>5,19; 6,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,66</t>
+          <t>6,22; 7,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,33; 13,07</t>
+          <t>11,38; 13,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 9,73</t>
+          <t>8,31; 9,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 21,5</t>
+          <t>6,51; 7,83</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>62449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33894</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90447</t>
+          <t>100839</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22282; 44166</t>
+          <t>22315; 45505</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74543; 111358</t>
+          <t>74339; 111990</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42692; 71527</t>
+          <t>42709; 71405</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42298; 76943</t>
+          <t>48375; 81723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18857; 39428</t>
+          <t>18743; 40165</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60243; 96430</t>
+          <t>59186; 95564</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34027; 62039</t>
+          <t>35553; 61485</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26535; 43371</t>
+          <t>29606; 49016</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46210; 79155</t>
+          <t>47157; 77525</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145688; 195522</t>
+          <t>145976; 197928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85652; 125367</t>
+          <t>84959; 124563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75231; 114505</t>
+          <t>83388; 121716</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>319194</t>
+          <t>85245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>62546</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>372463</t>
+          <t>147791</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35960; 64436</t>
+          <t>36384; 61463</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>107753; 150640</t>
+          <t>105137; 148812</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52552; 84382</t>
+          <t>51274; 84471</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83715; 703519</t>
+          <t>67910; 106458</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38635; 68041</t>
+          <t>40158; 68936</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89769; 128258</t>
+          <t>89460; 131150</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58926; 91112</t>
+          <t>59194; 93639</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41879; 67943</t>
+          <t>50315; 77388</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82344; 121086</t>
+          <t>82170; 123264</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207040; 265669</t>
+          <t>206589; 263758</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119785; 166695</t>
+          <t>118773; 165630</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>138456; 912564</t>
+          <t>126733; 171575</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52335</t>
+          <t>61316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>100539</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35861; 65875</t>
+          <t>35782; 63025</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73514; 111633</t>
+          <t>75885; 112324</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35027; 63136</t>
+          <t>35176; 64891</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37662; 73688</t>
+          <t>45301; 84257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26976; 50288</t>
+          <t>26803; 50805</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54188; 87729</t>
+          <t>52764; 85745</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30479; 56851</t>
+          <t>30508; 55922</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15744; 51308</t>
+          <t>29155; 52750</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69031; 105648</t>
+          <t>71095; 105913</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>136846; 187562</t>
+          <t>133288; 185233</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72431; 110187</t>
+          <t>74424; 111087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55966; 115207</t>
+          <t>80949; 125886</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71355</t>
+          <t>80170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>68872</t>
+          <t>71129</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>140227</t>
+          <t>151300</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36359; 61831</t>
+          <t>37183; 62764</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67853; 104518</t>
+          <t>66128; 101341</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59185; 93580</t>
+          <t>60213; 92509</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55798; 96427</t>
+          <t>63113; 99199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50808; 82835</t>
+          <t>51406; 81569</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73611; 110341</t>
+          <t>74177; 111997</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71957; 108609</t>
+          <t>73294; 110014</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52591; 90566</t>
+          <t>58459; 85274</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94415; 137193</t>
+          <t>94268; 134468</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>152377; 203309</t>
+          <t>149414; 200685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>142617; 192635</t>
+          <t>142334; 193210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>116446; 172800</t>
+          <t>130448; 176635</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>499437</t>
+          <t>289180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>190775</t>
+          <t>211289</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>690212</t>
+          <t>500469</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>151457; 203230</t>
+          <t>154159; 204118</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>355589; 432742</t>
+          <t>358780; 437270</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>216888; 279167</t>
+          <t>216282; 275981</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>264103; 1231091</t>
+          <t>256671; 328757</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>159488; 211701</t>
+          <t>159527; 212697</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>310960; 381103</t>
+          <t>312089; 383088</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>224481; 284889</t>
+          <t>224495; 283527</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>153103; 222707</t>
+          <t>188175; 238187</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>327531; 397914</t>
+          <t>323118; 399839</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>685550; 790818</t>
+          <t>688484; 796289</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>458366; 538181</t>
+          <t>459685; 546080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>441272; 1491175</t>
+          <t>457186; 550184</t>
         </is>
       </c>
     </row>
